--- a/6月银行导入模板分类清单.xlsx
+++ b/6月银行导入模板分类清单.xlsx
@@ -7,13 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="大单位汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="排除项清单" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部明细" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="映射规则" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="大单位汇总" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="排除项清单" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部明细" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'大单位汇总'!$A$1:$G$132</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'全部明细'!$A$1:$G$584</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'大单位汇总'!$A$1:$G$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'全部明细'!$A$1:$G$584</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,8 +57,23 @@
       <color rgb="00808080"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -87,6 +104,16 @@
         <bgColor rgb="00FFFBE6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -106,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -140,6 +167,28 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -505,6 +554,935 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="19" t="inlineStr">
+        <is>
+          <t>匹配方式</t>
+        </is>
+      </c>
+      <c r="C1" s="19" t="inlineStr">
+        <is>
+          <t>模式</t>
+        </is>
+      </c>
+      <c r="D1" s="19" t="inlineStr">
+        <is>
+          <t>大单位名</t>
+        </is>
+      </c>
+      <c r="E1" s="19" t="inlineStr">
+        <is>
+          <t>是否排除</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>prefix</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>吉林省交通实业发展有限公司</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr"/>
+      <c r="E2" s="20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>prefix</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>吉林省高等学校毕业生就业指导中心</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr"/>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>prefix</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>中建银（北京）房地产土地资产评估有限公司</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr"/>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>prefix</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>供销粮油吉林有限公司</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>prefix</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>平高集团华生电力设计有限公司</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>prefix</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>中国邮政储蓄银行股份有限公司吉林省分行直属支行</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>prefix</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>国家税务总局长春净月高新技术产业开发区税务局</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>prefix</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>中铁建大桥局六公司</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>中铁建大桥工程局集团第六工程有限公司</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>prefix</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>(吉林大学）</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>prefix</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>吉林大学第一医院</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>吉林大学第一医院</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>prefix</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>吉林大学第二医院</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>吉林大学第二医院</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>prefix</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>吉林大学口腔医院</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>吉林大学口腔医院</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>prefix</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>吉林大学中日联谊医院</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>吉林大学中日联谊医院</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>prefix</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>吉林大学</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>prefix</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>东北师范大学</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>东北师范大学</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>吉林省农业科学院</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>吉林省农业科学院</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>吉林省林业科学研究院</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>吉林省林业科学研究院</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>prefix</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>吉林银行</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr"/>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>中国铁建大桥工程局</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>中国铁建大桥工程局集团</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>中铁建大桥工程局集团第六工程有限公司</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>中铁建大桥工程局集团第六工程有限公司</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>中国检验认证</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>中国检验认证集团吉林分公司</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>吉林省交通科学研究所</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>吉林省交通科学研究所</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>吉林省交通规划设计院</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>吉林省交通规划设计院</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>吉林省假肢康复中心</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>吉林省假肢康复中心</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>吉林省工程技术学校</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>吉林省工程技术学校</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>吉林省戏曲剧院</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>吉林省戏曲剧院</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>吉林农业大学</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>吉林农业大学</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>吉林松辽</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>吉林松辽水资源开发有限责任公司</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>吉林省交通运输厅</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>吉林省交通运输厅</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>吉智科技</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>吉智科技研发（长春）有限公司</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>吉林粮食资产管理有限公司</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>吉林粮食资产管理有限公司</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>吉林建筑大学</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>吉林建筑大学</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>长春中医药大学</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>长春中医药大学</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>长春工业大学</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>长春工业大学</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>长春博众</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>长春博众汽车零部件有限责任公司</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>长春市公共关系学校</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>长春市公共关系学校</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>长春市城建工程学校</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>长春市城建工程学校</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>长春市九台区职业技术教育中心</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>长春市九台区职业技术教育中心</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>长春市得一物业服务有限公司</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>长春市得一物业服务有限公司</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>长春市体育彩票管理中心</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>长春市体育彩票管理中心</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>中铁津桥</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>中铁津桥工程检测有限公司</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>contains</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>天津弘创智融</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>天津弘创智融科技有限公司</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4605,7 +5583,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5675,7 +6653,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23911,4 +24889,168 @@
   <autoFilter ref="A1:G584"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="100" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>📋 映射规则使用说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>⚠ 规则是白名单机制：只有『映射规则』表中登记的规则才会触发合并。
+  不匹配任何规则的单位，直接按自身名称独立成组，不做大单位合并。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="24" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>『映射规则』sheet 控制大单位合并的归类逻辑。以下为各列说明：</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>【序号】  匹配优先级，从上到下依次检查，第一个匹配的规则生效。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         调整行顺序即可改变优先级。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="24" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>【匹配方式】  支持三种模式：</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="24" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  prefix     前缀匹配 — 单位名以「模式」开头即命中</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             例：prefix 吉林大学 → 吉林大学A、吉林大学B 均匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  contains   包含匹配 — 单位名含有「模式」即命中</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             例：contains 吉林省农业科学院 → XXX吉林省农业科学院XXX 匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  exact      精确匹配 — 单位名与「模式」完全相等才命中</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             例：exact 中铁建大桥局六公司 → 仅一字不差时匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>【大单位名】  命中规则后，该文件归入的大单位名称。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>【是否排除】  标记为 Y 的单位不参与大单位合并，</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             每个子单位独立成组输出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             常见排除项：外包业务、独立核算单位等。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="24" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>─── 编辑规则后保存即可，无需修改代码 ───</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>